--- a/schreuder-bonusan-pos/templates/zwolle.xlsx
+++ b/schreuder-bonusan-pos/templates/zwolle.xlsx
@@ -2750,7 +2750,7 @@
         <v>167</v>
       </c>
       <c r="B106" s="20">
-        <v>583</v>
+        <v>200583</v>
       </c>
       <c r="C106" s="7" t="s">
         <v>104</v>
